--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXVIII/LTAIPT_A63F38B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXXI-XL/FRACC XXXVIII/LTAIPT_A63F38B.xlsx
@@ -11,18 +11,20 @@
     <sheet name="Hidden_1" sheetId="2" r:id="rId2"/>
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
     <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
+    <sheet name="Hidden_4" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="Hidden_119">Hidden_1!$A$1:$A$26</definedName>
-    <definedName name="Hidden_223">Hidden_2!$A$1:$A$41</definedName>
-    <definedName name="Hidden_330">Hidden_3!$A$1:$A$32</definedName>
+    <definedName name="Hidden_117">Hidden_1!$A$1:$A$2</definedName>
+    <definedName name="Hidden_220">Hidden_2!$A$1:$A$26</definedName>
+    <definedName name="Hidden_324">Hidden_3!$A$1:$A$41</definedName>
+    <definedName name="Hidden_431">Hidden_4!$A$1:$A$32</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="226">
   <si>
     <t>49003</t>
   </si>
@@ -114,6 +116,9 @@
     <t>436869</t>
   </si>
   <si>
+    <t>571943</t>
+  </si>
+  <si>
     <t>436870</t>
   </si>
   <si>
@@ -237,6 +242,9 @@
     <t xml:space="preserve">Segundo apellido del responsable de la gestión del trámite </t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
     <t>Correo electrónico oficial</t>
   </si>
   <si>
@@ -309,24 +317,12 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>528D623DED8A7B50E2464BDFCE821D09</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t>Beca universal para estudiantes de educación media superior "Benito Juárez"</t>
   </si>
   <si>
-    <t>Becas</t>
-  </si>
-  <si>
     <t>No existe</t>
   </si>
   <si>
@@ -339,7 +335,7 @@
     <t>indefinido</t>
   </si>
   <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Control%20Escolar/1er_Trimestre/</t>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202022/Subdireccion%20Servicios%20Educativos/Beca_Universal_para_Estudiantes_de_Educacion_Media_Superior.pdf</t>
   </si>
   <si>
     <t>Nombre, fecha de nacimiento, curp, matrícula, teléfono, correo electrónico y escolaridad</t>
@@ -348,9 +344,6 @@
     <t/>
   </si>
   <si>
-    <t>http://cobatlaxcala.edu.mx/Transparencia/TRANSPARENCIA%202021/Subdireccion%20de%20Servicios%20Escolares/DOF%20-%20Diario%20Oficial%20de%20la%20Federaci%C3%B3n.pdf</t>
-  </si>
-  <si>
     <t>Griselda</t>
   </si>
   <si>
@@ -405,10 +398,31 @@
     <t>Subdirección de Servicios Educativos</t>
   </si>
   <si>
-    <t>06/10/2022</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 29 de agosto del  2022 al 27 de enero de 2023, el Colegio de Bachilleres del Estado de Tlaxcala, en el Programa de beca universal para estudiantes de educación media superior Benito Juárez, se encuentra de la siguiente manera: en la clave y denominación de partida presupuestal, los recursos son dispersados a los beneficiarios, directamente por la Coordinación Nacional de Becas para el Bienestar "Benito Juárez", por tanto no se tiene acceso a ello; los beneficiarios son ingresados por la dirección de cada plantel y aún se desconoce la manera en que haran llegar el recurso para  otorgarles su orden de pago y/o postulación y los jóvenes estudiantes acudan a realizar su cobro. Este proceso, depende del número de alumnos que se registren en la plataforma de becas, para después pasar a la validación que realiza la Coordinación Nacional de Becas para el Bienestar "Benito Juárez". No hay participación del Gobierno Estatal, sólo Federal. El monto es de $800.00 pesos mensuales no importando el género, el grado escolar ni el aprovechamiento académico. El presupuesto asignado al programa depende de la matrícula de alumnos vigente y puede variar cada semestre.</t>
+    <t>Becas Benito Juárez</t>
+  </si>
+  <si>
+    <t>875</t>
+  </si>
+  <si>
+    <t>Mujer</t>
+  </si>
+  <si>
+    <t>D0AB7A4170884E24B273D2EE0458A367</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>23/10/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 28 de agosto de 2023 al 26 de enero de 2024, el Colegio de Bachilleres del Estado de Tlaxcala, en el Programa de beca universal para estudiantes de educación media superior Benito Juárez, se encuentra de la siguiente manera: en la clave y denominación de partida presupuestal, los recursos son dispersados a los beneficiarios, directamente por la Coordinación Nacional de Becas para el Bienestar "Benito Juárez", por tanto no se tiene acceso a ello; los beneficiarios son ingresados por la dirección de cada plantel y aún se desconoce la manera en que haran llegar el recurso para  otorgarles su orden de pago y/o postulación y los jóvenes estudiantes acudan a realizar su cobro. Este proceso, depende del número de alumnos que se registren en la plataforma de becas, para después pasar a la validación que realiza la Coordinación Nacional de Becas para el Bienestar "Benito Juárez". No hay participación del Gobierno Estatal, sólo Federal. El monto es de $875.00 pesos mensuales no importando el género, el grado escolar ni el aprovechamiento académico. El presupuesto asignado al programa depende de la matrícula de alumnos vigente y puede variar cada semestre.</t>
+  </si>
+  <si>
+    <t>Hombre</t>
   </si>
   <si>
     <t>Carretera</t>
@@ -1080,10 +1094,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AO8"/>
+  <dimension ref="A1:AP8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -1093,45 +1107,46 @@
     <col min="8" max="8" width="70.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="158" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="153.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="75.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="158" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="153.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="42.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="48.85546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="50.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="33.5703125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="69.5703125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="61.140625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="20" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="255" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="37.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="69.5703125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="61.140625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="20" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1148,7 +1163,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -1163,7 +1178,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -1213,49 +1228,49 @@
         <v>6</v>
       </c>
       <c r="R4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="S4" t="s">
         <v>6</v>
       </c>
       <c r="T4" t="s">
+        <v>6</v>
+      </c>
+      <c r="U4" t="s">
         <v>11</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>8</v>
-      </c>
-      <c r="V4" t="s">
-        <v>6</v>
       </c>
       <c r="W4" t="s">
         <v>6</v>
       </c>
       <c r="X4" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y4" t="s">
         <v>11</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>8</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AA4" t="s">
         <v>6</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>8</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>6</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>8</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>6</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>11</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>6</v>
       </c>
       <c r="AG4" t="s">
         <v>6</v>
@@ -1273,19 +1288,22 @@
         <v>6</v>
       </c>
       <c r="AL4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AM4" t="s">
         <v>8</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AN4" t="s">
         <v>7</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AO4" t="s">
         <v>12</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AP4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:41" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -1406,10 +1424,13 @@
       <c r="AO5" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="AP5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1451,257 +1472,264 @@
       <c r="AM6" s="4"/>
       <c r="AN6" s="4"/>
       <c r="AO6" s="4"/>
-    </row>
-    <row r="7" spans="1:41" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="AP6" s="4"/>
+    </row>
+    <row r="7" spans="1:42" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG7" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH7" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AI7" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AK7" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AN7" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AO7" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:41" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="AP7" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:42" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="M8" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="X8" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="T8" s="2" t="s">
+      <c r="Y8" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="U8" s="2" t="s">
+      <c r="Z8" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="AA8" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="W8" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="X8" s="2" t="s">
+      <c r="AB8" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="AC8" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="AE8" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="Y8" s="2" t="s">
+      <c r="AF8" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="AG8" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="Z8" s="2" t="s">
+      <c r="AH8" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="AA8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AB8" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="AC8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AD8" s="2" t="s">
+      <c r="AI8" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AE8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="AF8" s="2" t="s">
+      <c r="AJ8" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="AG8" s="2" t="s">
+      <c r="AK8" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="AH8" s="2" t="s">
+      <c r="AL8" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="AI8" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="AJ8" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK8" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="AL8" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="AM8" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="AN8" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="AO8" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
+      </c>
+      <c r="AP8" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AO6"/>
+    <mergeCell ref="A6:AP6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1709,15 +1737,18 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="T8:T198">
-      <formula1>Hidden_119</formula1>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R8:R199">
+      <formula1>Hidden_117</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="X8:X198">
-      <formula1>Hidden_223</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="U8:U199">
+      <formula1>Hidden_220</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AE8:AE198">
-      <formula1>Hidden_330</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y8:Y199">
+      <formula1>Hidden_324</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF8:AF199">
+      <formula1>Hidden_431</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1726,137 +1757,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1866,212 +1777,137 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A41"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -2081,167 +1917,382 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>194</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
